--- a/synthetic_training_data_NRM_AST.xlsx
+++ b/synthetic_training_data_NRM_AST.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="synthetic_training_data" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">synthetic_training_data!$A$1:$A$1006</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">synthetic_training_data!$A$1:$A$977</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="178">
   <si>
     <t>document_code</t>
   </si>
@@ -205,13 +205,355 @@
   </si>
   <si>
     <t>She grows these vegetables herself and so has the right to sell them too</t>
+  </si>
+  <si>
+    <t>Some women whose husbands don’t stay in the village or those who are widows are responsible for their land</t>
+  </si>
+  <si>
+    <t>Men and women don’t have separate plots.</t>
+  </si>
+  <si>
+    <t>E.22</t>
+  </si>
+  <si>
+    <t>If her husband becomes rigid then she will not buy the land she so wants and will not let him buy the bike either</t>
+  </si>
+  <si>
+    <t>IN10E_M</t>
+  </si>
+  <si>
+    <t>Men buy plots in their wives’ names since by doing so they save on registration expenses</t>
+  </si>
+  <si>
+    <t>if the land belongs to the man, women cannot decide what to plant.</t>
+  </si>
+  <si>
+    <t>A woman cannot get a loan easily</t>
+  </si>
+  <si>
+    <t>Even if she works on the farm, the animals are counted as the husband’s property. except for chicken</t>
+  </si>
+  <si>
+    <t>women cannot go to borrow money if they do not own land.</t>
+  </si>
+  <si>
+    <t>Most women here farm the family's land. it is not hers</t>
+  </si>
+  <si>
+    <t>If her husband dies, the land goes to his brothers or his parents</t>
+  </si>
+  <si>
+    <t>when women inherit land, their husbands sort of owns it now</t>
+  </si>
+  <si>
+    <t>women work on the farm but they cannot sell it or borrow against it</t>
+  </si>
+  <si>
+    <t>if there is a large harvest, the man controls the money.</t>
+  </si>
+  <si>
+    <t>a woman can have ideas on what to grow but lacks the money to invest in the farm</t>
+  </si>
+  <si>
+    <t>A young married woman cannot take a loan on her own.</t>
+  </si>
+  <si>
+    <t>The title deed is usually in the father's or husband's name.</t>
+  </si>
+  <si>
+    <t>Women depend on husbands to get money for seeds and fertilizer.</t>
+  </si>
+  <si>
+    <t>Even when women earn money, the man still decides if she can make major purchases</t>
+  </si>
+  <si>
+    <t>Women here own chickens maybe, but not large livestock.</t>
+  </si>
+  <si>
+    <t>It is difficult for women to access tractors or motorized equipment because men are prioritized.</t>
+  </si>
+  <si>
+    <t>women remain at home, they do not go to public meetings about how to save or invest or take loans</t>
+  </si>
+  <si>
+    <t>if a married woman divorces she loses access to farmland.</t>
+  </si>
+  <si>
+    <t>Most farming equipment belongs to men.</t>
+  </si>
+  <si>
+    <t>Women contribute labour, but they do not own the income.</t>
+  </si>
+  <si>
+    <t>an unmarried woman struggles to access productive land - she has to lease and sometimes there is no money</t>
+  </si>
+  <si>
+    <t>If there is one bicycle or motorbike, the man uses it for business. the woman cannot use it</t>
+  </si>
+  <si>
+    <t>Women borrow small amounts from neighbours because that is the only way</t>
+  </si>
+  <si>
+    <t>Men decide how profits from crops are used.</t>
+  </si>
+  <si>
+    <t>very few women in this village can say they truly own productive assets.</t>
+  </si>
+  <si>
+    <t>land is not registered in the woman's name</t>
+  </si>
+  <si>
+    <t>the husband buys the farming inputs that he wants not what the woman wants</t>
+  </si>
+  <si>
+    <t>Many women fear loans because what if they cannot repay?</t>
+  </si>
+  <si>
+    <t>Women need permission before using family resources.</t>
+  </si>
+  <si>
+    <t>Most women cannot afford to hire irrigation equipment on their own.</t>
+  </si>
+  <si>
+    <t>some husbands also want to control the money that the wives have</t>
+  </si>
+  <si>
+    <t>Women work hard in agriculture but own very little.</t>
+  </si>
+  <si>
+    <t>If the government compensates families for the land taken, the man takes all the money</t>
+  </si>
+  <si>
+    <t>even when husband is away in another village for work, the woman has to consult with him on everything about the farm</t>
+  </si>
+  <si>
+    <t>Widows can continue farming on their husband's land but they know they do not own it- the in-laws can take it away anytime</t>
+  </si>
+  <si>
+    <t>if a woman has no sons, she cannot claim the family land.</t>
+  </si>
+  <si>
+    <t>Some husbands do not allow wives to join village savings groups.</t>
+  </si>
+  <si>
+    <t>most agricultural officers that are male discuss a lot of things about money with the men not with women</t>
+  </si>
+  <si>
+    <t>a woman struggles to expand their farming activities because of lacking money</t>
+  </si>
+  <si>
+    <t>A woman may save money secretly because she cannot freely save or use it- yet it is hers.</t>
+  </si>
+  <si>
+    <t>people here do not think women's farming activities are important or serious to finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the credit groups for women help women get small loans </t>
+  </si>
+  <si>
+    <t>a woman can buy land here in her own names</t>
+  </si>
+  <si>
+    <t>a woman take agricultural loans without needing permission from husbands if she has the means to repay it</t>
+  </si>
+  <si>
+    <t>Women and men jointly decide how to use farm income.</t>
+  </si>
+  <si>
+    <t>some women in this village own cows and other livestock just like the men.</t>
+  </si>
+  <si>
+    <t>Women can inherit land from their parents.</t>
+  </si>
+  <si>
+    <t>Women farmers can join cooperatives and access credit.</t>
+  </si>
+  <si>
+    <t>women borrowers repay on time - so they can get small loans</t>
+  </si>
+  <si>
+    <t>even women can participate in farmer associations and savings groups.</t>
+  </si>
+  <si>
+    <t>if a husband wants to register land jointly with his wife, he can do it.</t>
+  </si>
+  <si>
+    <t>Sometimes, women have enough money to buy seeds and fertilizer themselves.</t>
+  </si>
+  <si>
+    <t>A woman can start farming independently if she has the skills.</t>
+  </si>
+  <si>
+    <t>Women traders here get small loans to expand their small market businesses</t>
+  </si>
+  <si>
+    <t>Women control the income from the crops they grow.</t>
+  </si>
+  <si>
+    <t>Some women can afford to hire labourers for their farms.</t>
+  </si>
+  <si>
+    <t>Women are active members of cooperatives.</t>
+  </si>
+  <si>
+    <t>through women's groups, women can access small machinery and irrigation pumps.</t>
+  </si>
+  <si>
+    <t>as a group, women can approach lending institutions and get loans for farming or other acrivities</t>
+  </si>
+  <si>
+    <t>even widows manage their farms by themselves</t>
+  </si>
+  <si>
+    <t>Families also alow daughters to inherit land just like their sons</t>
+  </si>
+  <si>
+    <t>Women decide how to spend earnings from farming without asking for permission</t>
+  </si>
+  <si>
+    <t>savings groups have strengthened women financially</t>
+  </si>
+  <si>
+    <t>both men and women attend agricultural finance trainings</t>
+  </si>
+  <si>
+    <t>A married woman can take a loan in her own name.</t>
+  </si>
+  <si>
+    <t>Women farmers here are respected because they also contribute to household income.</t>
+  </si>
+  <si>
+    <t>Women can own livestock and sell animals when needed.</t>
+  </si>
+  <si>
+    <t>projects in this area prioritize women’s access to inputs</t>
+  </si>
+  <si>
+    <t>here, women are recognized as farm managers not just for providing labor</t>
+  </si>
+  <si>
+    <t>It is normal now for women to start farming businesses.</t>
+  </si>
+  <si>
+    <t>Women leaders in the cooperative or savings group help other women access loans and land.</t>
+  </si>
+  <si>
+    <t>Women participate in decisions about buying and selling land.</t>
+  </si>
+  <si>
+    <t>if a woman has a phone, she can also use mobile banking services to manage her income.</t>
+  </si>
+  <si>
+    <t>Many women here have their some savings.</t>
+  </si>
+  <si>
+    <t>in some places, women can access extension services and credit directly.</t>
+  </si>
+  <si>
+    <t>Daughters also inherit productive assets</t>
+  </si>
+  <si>
+    <t>when women have legal ownership of the land, they feel more secure</t>
+  </si>
+  <si>
+    <t>Women’s groups pool resources to buy farming equipment that the women in the group can use</t>
+  </si>
+  <si>
+    <t>Banks actively encourage women farmers to apply for loans.</t>
+  </si>
+  <si>
+    <t>Husbands and wives who own assets together make farming decisions together.</t>
+  </si>
+  <si>
+    <t>Women use their small loans to improve production on their farms</t>
+  </si>
+  <si>
+    <t>even female-headed households farm independently and successfully.</t>
+  </si>
+  <si>
+    <t>some women own bicycles to help take their goods to the market when there is no man available to help</t>
+  </si>
+  <si>
+    <t>Women can easily join village savings and loan groups.</t>
+  </si>
+  <si>
+    <t>Some women can afford to hire labour from both men and women on their farms.</t>
+  </si>
+  <si>
+    <t>married women can buy land on their own or with their husbands and their names are on the records</t>
+  </si>
+  <si>
+    <t>Women can freely negotiate with traders and buyers.</t>
+  </si>
+  <si>
+    <t>Women now have better access to financial information than before hrough social networks</t>
+  </si>
+  <si>
+    <t>most women would say they can access some form of credit.</t>
+  </si>
+  <si>
+    <t>PK5E_M</t>
+  </si>
+  <si>
+    <t>She can force her husband for a particular type of seed good for bread baking and also for the seeds that are free of impurities</t>
+  </si>
+  <si>
+    <t>If she brings in profit, then the man will not say anything</t>
+  </si>
+  <si>
+    <t>In this community it is not possible if she want to sell her poultry products or embroidery outside the village herself, but selling within the village is not a problem</t>
+  </si>
+  <si>
+    <t>She can sell her products through someone else (male)</t>
+  </si>
+  <si>
+    <t>The household head decides who is to be given which plot</t>
+  </si>
+  <si>
+    <t>There are no separate plots for husband and wife generally in this community</t>
+  </si>
+  <si>
+    <t>A woman can ask her relatives to give her plot to rent or give her land on contract/lease</t>
+  </si>
+  <si>
+    <t>E.24</t>
+  </si>
+  <si>
+    <t>in our culture, a woman cannot own anything alone</t>
+  </si>
+  <si>
+    <t>some wives are allowed to do their own business, as they like</t>
+  </si>
+  <si>
+    <t>E.25</t>
+  </si>
+  <si>
+    <t>if the husband does not want her to to sell herself, she can sell through someone else - a male in the family</t>
+  </si>
+  <si>
+    <t>even if she has her own plot, she might not get time to work on it, if there is a lot of work on the husband's plot</t>
+  </si>
+  <si>
+    <t>E.27</t>
+  </si>
+  <si>
+    <t>she has her own plot and can work on her usband's when she has time</t>
+  </si>
+  <si>
+    <t>NRM_AST_0</t>
+  </si>
+  <si>
+    <t>the husband will say good, you have brought profit, you earn, I will look after the kids</t>
+  </si>
+  <si>
+    <t>E.30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -229,6 +571,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="'Segoe UI'"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -253,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -269,8 +621,11 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
@@ -660,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>26</v>
@@ -689,7 +1044,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>26</v>
@@ -718,7 +1073,7 @@
         <v>32</v>
       </c>
       <c r="G8" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>26</v>
@@ -747,7 +1102,7 @@
         <v>34</v>
       </c>
       <c r="G9" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>26</v>
@@ -863,7 +1218,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>26</v>
@@ -921,7 +1276,7 @@
         <v>43</v>
       </c>
       <c r="G15" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>26</v>
@@ -1008,7 +1363,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>26</v>
@@ -1037,7 +1392,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>26</v>
@@ -1095,7 +1450,7 @@
         <v>54</v>
       </c>
       <c r="G21" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>26</v>
@@ -1153,7 +1508,7 @@
         <v>59</v>
       </c>
       <c r="G23" s="5">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>26</v>
@@ -1170,7 +1525,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>61</v>
@@ -1182,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="G24" s="5">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>26</v>
@@ -1192,19 +1547,26 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="4"/>
+      <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C25" s="3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="1">
-        <v>0.9</v>
+      <c r="G25" s="5">
+        <v>0.95</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>26</v>
@@ -1214,1236 +1576,2706 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4"/>
+      <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="D26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="4"/>
+      <c r="G26" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="3"/>
-      <c r="H27" s="4"/>
+      <c r="A27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="3"/>
-      <c r="H28" s="4"/>
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
+      <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F31" s="3"/>
-      <c r="H31" s="4"/>
+      <c r="G31" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="3"/>
-      <c r="H32" s="4"/>
+      <c r="A32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="A33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="34">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="36">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="37">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="4"/>
+      <c r="A37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F37" s="3"/>
-      <c r="H37" s="4"/>
+      <c r="G37" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="38">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="4"/>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F38" s="3"/>
-      <c r="H38" s="4"/>
+      <c r="G38" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="39">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="4"/>
+      <c r="A39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F39" s="3"/>
-      <c r="H39" s="4"/>
+      <c r="G39" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="40">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="4"/>
+      <c r="A40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F40" s="3"/>
-      <c r="H40" s="4"/>
+      <c r="G40" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="41">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="4"/>
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F41" s="3"/>
-      <c r="H41" s="4"/>
+      <c r="G41" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="4"/>
+      <c r="A42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F42" s="3"/>
-      <c r="H42" s="4"/>
+      <c r="G42" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="43">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="4"/>
+      <c r="A43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F43" s="3"/>
-      <c r="H43" s="4"/>
+      <c r="G43" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="44">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="4"/>
+      <c r="A44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F44" s="3"/>
-      <c r="H44" s="4"/>
+      <c r="G44" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="4"/>
+      <c r="A45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F45" s="3"/>
-      <c r="H45" s="4"/>
+      <c r="G45" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="46">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="4"/>
+      <c r="A46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F46" s="3"/>
-      <c r="H46" s="4"/>
+      <c r="G46" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="4"/>
+      <c r="A47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F47" s="3"/>
-      <c r="H47" s="4"/>
+      <c r="G47" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="4"/>
+      <c r="A48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F48" s="3"/>
-      <c r="H48" s="4"/>
+      <c r="G48" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="4"/>
+      <c r="A49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F49" s="3"/>
-      <c r="H49" s="4"/>
+      <c r="G49" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="4"/>
+      <c r="A50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F50" s="3"/>
-      <c r="H50" s="4"/>
+      <c r="G50" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="4"/>
+      <c r="A51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F51" s="3"/>
-      <c r="H51" s="4"/>
+      <c r="G51" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="4"/>
+      <c r="A52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F52" s="3"/>
-      <c r="H52" s="4"/>
+      <c r="G52" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="4"/>
+      <c r="A53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F53" s="3"/>
-      <c r="H53" s="4"/>
+      <c r="G53" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="4"/>
+      <c r="A54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F54" s="3"/>
-      <c r="H54" s="4"/>
+      <c r="G54" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="4"/>
+      <c r="A55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F55" s="3"/>
-      <c r="H55" s="4"/>
+      <c r="G55" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="4"/>
+      <c r="A56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F56" s="3"/>
-      <c r="H56" s="4"/>
+      <c r="G56" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="4"/>
+      <c r="A57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F57" s="3"/>
-      <c r="H57" s="4"/>
+      <c r="G57" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="4"/>
+      <c r="A58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F58" s="3"/>
-      <c r="H58" s="4"/>
+      <c r="G58" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="4"/>
+      <c r="A59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F59" s="3"/>
-      <c r="H59" s="4"/>
+      <c r="G59" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="4"/>
+      <c r="A60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F60" s="3"/>
-      <c r="H60" s="4"/>
+      <c r="G60" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="4"/>
+      <c r="A61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F61" s="3"/>
-      <c r="H61" s="4"/>
+      <c r="G61" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="4"/>
+      <c r="A62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F62" s="3"/>
-      <c r="H62" s="4"/>
+      <c r="G62" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="4"/>
+      <c r="A63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F63" s="3"/>
-      <c r="H63" s="4"/>
+      <c r="G63" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="4"/>
+      <c r="A64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F64" s="3"/>
-      <c r="H64" s="4"/>
+      <c r="G64" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="4"/>
+      <c r="A65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F65" s="3"/>
-      <c r="H65" s="4"/>
+      <c r="G65" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="66">
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="4"/>
+      <c r="A66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F66" s="3"/>
-      <c r="H66" s="4"/>
+      <c r="G66" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="67">
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="4"/>
+      <c r="A67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F67" s="3"/>
-      <c r="H67" s="4"/>
+      <c r="G67" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="4"/>
+      <c r="A68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F68" s="3"/>
-      <c r="H68" s="4"/>
+      <c r="G68" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="4"/>
+      <c r="A69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F69" s="3"/>
-      <c r="H69" s="4"/>
+      <c r="G69" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="4"/>
+      <c r="A70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F70" s="3"/>
-      <c r="H70" s="4"/>
+      <c r="G70" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="4"/>
+      <c r="A71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F71" s="3"/>
-      <c r="H71" s="4"/>
+      <c r="G71" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="4"/>
+      <c r="A72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F72" s="3"/>
-      <c r="H72" s="4"/>
+      <c r="G72" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="4"/>
+      <c r="A73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F73" s="3"/>
-      <c r="H73" s="4"/>
+      <c r="G73" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="4"/>
+      <c r="A74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F74" s="3"/>
-      <c r="H74" s="4"/>
+      <c r="G74" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="4"/>
+      <c r="A75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F75" s="3"/>
-      <c r="H75" s="4"/>
+      <c r="G75" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="4"/>
+      <c r="A76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F76" s="3"/>
-      <c r="H76" s="4"/>
+      <c r="G76" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="4"/>
+      <c r="A77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F77" s="3"/>
-      <c r="H77" s="4"/>
+      <c r="G77" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="4"/>
+      <c r="A78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F78" s="3"/>
-      <c r="H78" s="4"/>
+      <c r="G78" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="4"/>
+      <c r="A79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F79" s="3"/>
-      <c r="H79" s="4"/>
+      <c r="G79" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="4"/>
+      <c r="A80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F80" s="3"/>
-      <c r="H80" s="4"/>
+      <c r="G80" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="4"/>
+      <c r="A81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F81" s="3"/>
-      <c r="H81" s="4"/>
+      <c r="G81" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="4"/>
+      <c r="A82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F82" s="3"/>
-      <c r="H82" s="4"/>
+      <c r="G82" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="4"/>
+      <c r="A83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F83" s="3"/>
-      <c r="H83" s="4"/>
+      <c r="G83" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="4"/>
+      <c r="A84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F84" s="3"/>
-      <c r="H84" s="4"/>
+      <c r="G84" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="4"/>
+      <c r="A85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F85" s="3"/>
-      <c r="H85" s="4"/>
+      <c r="G85" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="4"/>
+      <c r="A86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F86" s="3"/>
-      <c r="H86" s="4"/>
+      <c r="G86" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="4"/>
+      <c r="A87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F87" s="3"/>
-      <c r="H87" s="4"/>
+      <c r="G87" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="4"/>
+      <c r="A88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F88" s="3"/>
-      <c r="H88" s="4"/>
+      <c r="G88" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="4"/>
+      <c r="A89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F89" s="3"/>
-      <c r="H89" s="4"/>
+      <c r="G89" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="4"/>
+      <c r="A90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F90" s="3"/>
-      <c r="H90" s="4"/>
+      <c r="G90" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="4"/>
+      <c r="A91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F91" s="3"/>
-      <c r="H91" s="4"/>
+      <c r="G91" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="4"/>
+      <c r="A92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F92" s="3"/>
-      <c r="H92" s="4"/>
+      <c r="G92" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="4"/>
+      <c r="A93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F93" s="3"/>
-      <c r="H93" s="4"/>
+      <c r="G93" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="4"/>
+      <c r="A94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F94" s="3"/>
-      <c r="H94" s="4"/>
+      <c r="G94" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="4"/>
+      <c r="A95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F95" s="3"/>
-      <c r="H95" s="4"/>
+      <c r="G95" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="4"/>
+      <c r="A96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F96" s="3"/>
-      <c r="H96" s="4"/>
+      <c r="G96" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
+      <c r="A97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F97" s="3"/>
-      <c r="H97" s="4"/>
+      <c r="G97" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
+      <c r="A98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F98" s="3"/>
-      <c r="H98" s="4"/>
+      <c r="G98" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
+      <c r="A99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F99" s="3"/>
-      <c r="H99" s="4"/>
+      <c r="G99" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
+      <c r="A100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F100" s="3"/>
-      <c r="H100" s="4"/>
+      <c r="G100" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
+      <c r="A101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F101" s="3"/>
-      <c r="H101" s="4"/>
+      <c r="G101" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
+      <c r="A102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F102" s="3"/>
-      <c r="H102" s="4"/>
+      <c r="G102" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
+      <c r="A103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F103" s="3"/>
-      <c r="H103" s="4"/>
+      <c r="G103" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
+      <c r="A104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F104" s="3"/>
-      <c r="H104" s="4"/>
+      <c r="G104" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
+      <c r="A105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F105" s="3"/>
-      <c r="H105" s="4"/>
+      <c r="G105" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
+      <c r="A106" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F106" s="3"/>
-      <c r="H106" s="4"/>
+      <c r="G106" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
+      <c r="A107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F107" s="3"/>
-      <c r="H107" s="4"/>
+      <c r="G107" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
+      <c r="A108" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F108" s="3"/>
-      <c r="H108" s="4"/>
+      <c r="G108" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
+      <c r="A109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F109" s="3"/>
-      <c r="H109" s="4"/>
+      <c r="G109" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
+      <c r="A110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F110" s="3"/>
-      <c r="H110" s="4"/>
+      <c r="G110" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
+      <c r="A111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F111" s="3"/>
-      <c r="H111" s="4"/>
+      <c r="G111" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
+      <c r="A112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F112" s="3"/>
-      <c r="H112" s="4"/>
+      <c r="G112" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
+      <c r="A113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F113" s="3"/>
-      <c r="H113" s="4"/>
+      <c r="G113" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
+      <c r="A114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F114" s="3"/>
-      <c r="H114" s="4"/>
+      <c r="G114" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
+      <c r="A115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F115" s="3"/>
-      <c r="H115" s="4"/>
+      <c r="G115" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
+      <c r="A116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F116" s="3"/>
-      <c r="H116" s="4"/>
+      <c r="G116" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
+      <c r="A117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F117" s="3"/>
-      <c r="H117" s="4"/>
+      <c r="G117" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
+      <c r="A118" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F118" s="3"/>
-      <c r="H118" s="4"/>
+      <c r="G118" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
+      <c r="A119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F119" s="3"/>
-      <c r="H119" s="4"/>
+      <c r="G119" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="H120" s="4"/>
+      <c r="A120" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G120" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="H121" s="4"/>
+      <c r="A121" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G121" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="H122" s="4"/>
+      <c r="A122" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G122" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
-      <c r="H123" s="4"/>
+      <c r="A123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G123" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="H124" s="4"/>
+      <c r="A124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G124" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
-      <c r="H125" s="4"/>
+      <c r="A125" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G125" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="H126" s="4"/>
+      <c r="A126" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G126" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="H127" s="4"/>
+      <c r="A127" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G127" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
-      <c r="H128" s="4"/>
+      <c r="A128" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G128" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="H129" s="4"/>
+      <c r="A129" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G129" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
-      <c r="H130" s="4"/>
+      <c r="A130" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G130" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-      <c r="H131" s="4"/>
+      <c r="A131" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G131" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-      <c r="H132" s="4"/>
+      <c r="A132" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G132" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="7"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
       <c r="H133" s="4"/>
     </row>
     <row r="134">
-      <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
-      <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="7"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
       <c r="H134" s="4"/>
     </row>
     <row r="135">
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="6"/>
+      <c r="D135" s="7"/>
       <c r="E135" s="3"/>
       <c r="H135" s="4"/>
     </row>
     <row r="136">
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="6"/>
+      <c r="D136" s="7"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
       <c r="H136" s="4"/>
     </row>
     <row r="137">
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
-      <c r="D137" s="6"/>
+      <c r="D137" s="7"/>
       <c r="E137" s="3"/>
       <c r="H137" s="4"/>
     </row>
     <row r="138">
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
-      <c r="D138" s="6"/>
+      <c r="D138" s="7"/>
       <c r="E138" s="3"/>
       <c r="H138" s="4"/>
     </row>
     <row r="139">
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
-      <c r="D139" s="6"/>
+      <c r="D139" s="7"/>
       <c r="E139" s="3"/>
       <c r="H139" s="4"/>
     </row>
     <row r="140">
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
-      <c r="D140" s="6"/>
+      <c r="D140" s="7"/>
       <c r="E140" s="3"/>
       <c r="H140" s="4"/>
     </row>
     <row r="141">
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
-      <c r="D141" s="6"/>
+      <c r="D141" s="3"/>
       <c r="E141" s="3"/>
       <c r="H141" s="4"/>
     </row>
     <row r="142">
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
-      <c r="D142" s="6"/>
+      <c r="D142" s="3"/>
       <c r="E142" s="3"/>
       <c r="H142" s="4"/>
     </row>
     <row r="143">
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
-      <c r="D143" s="6"/>
+      <c r="D143" s="3"/>
       <c r="E143" s="3"/>
       <c r="H143" s="4"/>
     </row>
     <row r="144">
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
-      <c r="D144" s="6"/>
+      <c r="D144" s="3"/>
       <c r="E144" s="3"/>
       <c r="H144" s="4"/>
     </row>
-    <row r="145">
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="3"/>
-      <c r="H145" s="4"/>
-    </row>
-    <row r="146">
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="3"/>
-      <c r="H146" s="4"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="3"/>
-      <c r="H147" s="4"/>
-    </row>
-    <row r="148">
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="3"/>
-      <c r="H148" s="4"/>
-    </row>
-    <row r="149">
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="3"/>
-      <c r="H149" s="4"/>
-    </row>
-    <row r="150">
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="3"/>
-      <c r="H150" s="4"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="3"/>
-      <c r="H151" s="4"/>
-    </row>
-    <row r="152">
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="3"/>
-      <c r="H152" s="4"/>
-    </row>
-    <row r="153">
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="3"/>
-      <c r="H153" s="4"/>
-    </row>
-    <row r="154">
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="3"/>
-      <c r="H154" s="4"/>
-    </row>
-    <row r="155">
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="3"/>
-      <c r="H155" s="4"/>
-    </row>
-    <row r="156">
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="3"/>
-      <c r="H156" s="4"/>
-    </row>
-    <row r="157">
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="3"/>
-      <c r="H157" s="4"/>
-    </row>
-    <row r="158">
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="3"/>
-      <c r="H158" s="4"/>
-    </row>
-    <row r="159">
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="3"/>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160">
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="3"/>
-      <c r="H160" s="4"/>
-    </row>
-    <row r="161">
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="3"/>
-      <c r="H161" s="4"/>
-    </row>
-    <row r="162">
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="3"/>
-      <c r="H162" s="4"/>
-    </row>
-    <row r="163">
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="3"/>
-      <c r="H163" s="4"/>
-    </row>
-    <row r="164">
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="3"/>
-      <c r="H164" s="4"/>
-    </row>
-    <row r="165">
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="3"/>
-      <c r="H165" s="4"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="3"/>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167">
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="3"/>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168">
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="3"/>
-      <c r="H168" s="4"/>
-    </row>
-    <row r="169">
-      <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="3"/>
-      <c r="H169" s="4"/>
-    </row>
-    <row r="170">
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-      <c r="H170" s="4"/>
-    </row>
-    <row r="171">
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-      <c r="H171" s="4"/>
-    </row>
-    <row r="172">
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-      <c r="H172" s="4"/>
-    </row>
-    <row r="173">
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3"/>
-      <c r="H173" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$A$1006"/>
+  <autoFilter ref="$A$1:$A$977"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>